--- a/artfynd/A 174-2021 artfynd.xlsx
+++ b/artfynd/A 174-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 174-2021 artfynd.xlsx
+++ b/artfynd/A 174-2021 artfynd.xlsx
@@ -1763,10 +1763,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101434957</v>
+        <v>101434950</v>
       </c>
       <c r="B11" t="n">
-        <v>57963</v>
+        <v>57656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1779,16 +1779,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,10 +1883,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101434950</v>
+        <v>101434957</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57963</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 174-2021 artfynd.xlsx
+++ b/artfynd/A 174-2021 artfynd.xlsx
@@ -1763,10 +1763,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101434950</v>
+        <v>101434957</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57964</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1779,16 +1779,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,10 +1883,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101434957</v>
+        <v>101434950</v>
       </c>
       <c r="B12" t="n">
-        <v>57963</v>
+        <v>57657</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,16 +1899,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 174-2021 artfynd.xlsx
+++ b/artfynd/A 174-2021 artfynd.xlsx
@@ -2411,7 +2411,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676068</v>
+        <v>119676067</v>
       </c>
       <c r="B17" t="n">
         <v>79643</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425762</v>
+        <v>425903</v>
       </c>
       <c r="R17" t="n">
-        <v>6910277</v>
+        <v>6910428</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119676067</v>
+        <v>119676068</v>
       </c>
       <c r="B18" t="n">
         <v>79643</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425903</v>
+        <v>425762</v>
       </c>
       <c r="R18" t="n">
-        <v>6910428</v>
+        <v>6910277</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 174-2021 artfynd.xlsx
+++ b/artfynd/A 174-2021 artfynd.xlsx
@@ -2003,10 +2003,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676079</v>
+        <v>119676063</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>79636</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2015,25 +2015,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425799</v>
+        <v>425949</v>
       </c>
       <c r="R13" t="n">
-        <v>6910306</v>
+        <v>6910412</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2309,10 +2309,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119676080</v>
+        <v>119676067</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2321,25 +2321,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425773</v>
+        <v>425903</v>
       </c>
       <c r="R16" t="n">
-        <v>6910447</v>
+        <v>6910428</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2411,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676067</v>
+        <v>119676079</v>
       </c>
       <c r="B17" t="n">
-        <v>79643</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,25 +2423,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425903</v>
+        <v>425799</v>
       </c>
       <c r="R17" t="n">
-        <v>6910428</v>
+        <v>6910306</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119676068</v>
+        <v>119676083</v>
       </c>
       <c r="B18" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425762</v>
+        <v>425821</v>
       </c>
       <c r="R18" t="n">
-        <v>6910277</v>
+        <v>6910390</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119676083</v>
+        <v>119676080</v>
       </c>
       <c r="B19" t="n">
         <v>78526</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425821</v>
+        <v>425773</v>
       </c>
       <c r="R19" t="n">
-        <v>6910390</v>
+        <v>6910447</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676060</v>
+        <v>119676068</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>79643</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425934</v>
+        <v>425762</v>
       </c>
       <c r="R20" t="n">
-        <v>6910417</v>
+        <v>6910277</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2921,10 +2921,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676063</v>
+        <v>119676088</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2933,25 +2933,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425949</v>
+        <v>425913</v>
       </c>
       <c r="R22" t="n">
-        <v>6910412</v>
+        <v>6910421</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3125,7 +3125,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676088</v>
+        <v>119676089</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425913</v>
+        <v>425930</v>
       </c>
       <c r="R24" t="n">
-        <v>6910421</v>
+        <v>6910423</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676089</v>
+        <v>119676060</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3239,25 +3239,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425930</v>
+        <v>425934</v>
       </c>
       <c r="R25" t="n">
-        <v>6910423</v>
+        <v>6910417</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 174-2021 artfynd.xlsx
+++ b/artfynd/A 174-2021 artfynd.xlsx
@@ -2105,10 +2105,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676086</v>
+        <v>119676078</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2121,21 +2121,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>425769</v>
+        <v>425921</v>
       </c>
       <c r="R14" t="n">
-        <v>6910364</v>
+        <v>6910435</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119676078</v>
+        <v>119676079</v>
       </c>
       <c r="B15" t="n">
         <v>90580</v>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>425921</v>
+        <v>425799</v>
       </c>
       <c r="R15" t="n">
-        <v>6910435</v>
+        <v>6910306</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2309,10 +2309,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119676067</v>
+        <v>119676080</v>
       </c>
       <c r="B16" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2321,25 +2321,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425903</v>
+        <v>425773</v>
       </c>
       <c r="R16" t="n">
-        <v>6910428</v>
+        <v>6910447</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2411,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676079</v>
+        <v>119676060</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
+        <v>79636</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,25 +2423,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425799</v>
+        <v>425934</v>
       </c>
       <c r="R17" t="n">
-        <v>6910306</v>
+        <v>6910417</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119676083</v>
+        <v>119676086</v>
       </c>
       <c r="B18" t="n">
         <v>78526</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425821</v>
+        <v>425769</v>
       </c>
       <c r="R18" t="n">
-        <v>6910390</v>
+        <v>6910364</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119676080</v>
+        <v>119676068</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2627,25 +2627,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425773</v>
+        <v>425762</v>
       </c>
       <c r="R19" t="n">
-        <v>6910447</v>
+        <v>6910277</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2717,7 +2717,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676068</v>
+        <v>119676067</v>
       </c>
       <c r="B20" t="n">
         <v>79643</v>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425762</v>
+        <v>425903</v>
       </c>
       <c r="R20" t="n">
-        <v>6910277</v>
+        <v>6910428</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676088</v>
+        <v>119676089</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425913</v>
+        <v>425930</v>
       </c>
       <c r="R22" t="n">
-        <v>6910421</v>
+        <v>6910423</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3125,7 +3125,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676089</v>
+        <v>119676088</v>
       </c>
       <c r="B24" t="n">
         <v>78526</v>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425930</v>
+        <v>425913</v>
       </c>
       <c r="R24" t="n">
-        <v>6910423</v>
+        <v>6910421</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676060</v>
+        <v>119676083</v>
       </c>
       <c r="B25" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3239,25 +3239,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425934</v>
+        <v>425821</v>
       </c>
       <c r="R25" t="n">
-        <v>6910417</v>
+        <v>6910390</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 174-2021 artfynd.xlsx
+++ b/artfynd/A 174-2021 artfynd.xlsx
@@ -2003,10 +2003,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119676063</v>
+        <v>119676079</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2015,25 +2015,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>425949</v>
+        <v>425799</v>
       </c>
       <c r="R13" t="n">
-        <v>6910412</v>
+        <v>6910306</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119676078</v>
+        <v>119676060</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>79636</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2117,25 +2117,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2145,10 +2145,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>425921</v>
+        <v>425934</v>
       </c>
       <c r="R14" t="n">
-        <v>6910435</v>
+        <v>6910417</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2207,10 +2207,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119676079</v>
+        <v>119676083</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2223,21 +2223,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>425799</v>
+        <v>425821</v>
       </c>
       <c r="R15" t="n">
-        <v>6910306</v>
+        <v>6910390</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119676080</v>
+        <v>119676089</v>
       </c>
       <c r="B16" t="n">
         <v>78526</v>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>425773</v>
+        <v>425930</v>
       </c>
       <c r="R16" t="n">
-        <v>6910447</v>
+        <v>6910423</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2411,7 +2411,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119676060</v>
+        <v>119676062</v>
       </c>
       <c r="B17" t="n">
         <v>79636</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>425934</v>
+        <v>425826</v>
       </c>
       <c r="R17" t="n">
-        <v>6910417</v>
+        <v>6910390</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119676086</v>
+        <v>119676068</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2525,25 +2525,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>425769</v>
+        <v>425762</v>
       </c>
       <c r="R18" t="n">
-        <v>6910364</v>
+        <v>6910277</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119676068</v>
+        <v>119676063</v>
       </c>
       <c r="B19" t="n">
-        <v>79643</v>
+        <v>79636</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>425762</v>
+        <v>425949</v>
       </c>
       <c r="R19" t="n">
-        <v>6910277</v>
+        <v>6910412</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119676067</v>
+        <v>119676057</v>
       </c>
       <c r="B20" t="n">
-        <v>79643</v>
+        <v>104994</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>425903</v>
+        <v>425863</v>
       </c>
       <c r="R20" t="n">
-        <v>6910428</v>
+        <v>6910382</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119676062</v>
+        <v>119676078</v>
       </c>
       <c r="B21" t="n">
-        <v>79636</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2831,25 +2831,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>425826</v>
+        <v>425921</v>
       </c>
       <c r="R21" t="n">
-        <v>6910390</v>
+        <v>6910435</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119676089</v>
+        <v>119676088</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>425930</v>
+        <v>425913</v>
       </c>
       <c r="R22" t="n">
-        <v>6910423</v>
+        <v>6910421</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119676057</v>
+        <v>119676080</v>
       </c>
       <c r="B23" t="n">
-        <v>104994</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3035,25 +3035,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>425863</v>
+        <v>425773</v>
       </c>
       <c r="R23" t="n">
-        <v>6910382</v>
+        <v>6910447</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119676088</v>
+        <v>119676067</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3137,25 +3137,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>425913</v>
+        <v>425903</v>
       </c>
       <c r="R24" t="n">
-        <v>6910421</v>
+        <v>6910428</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119676083</v>
+        <v>119676086</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>425821</v>
+        <v>425769</v>
       </c>
       <c r="R25" t="n">
-        <v>6910390</v>
+        <v>6910364</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>

--- a/artfynd/A 174-2021 artfynd.xlsx
+++ b/artfynd/A 174-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3327,6 +3327,142 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121592572</v>
+      </c>
+      <c r="B26" t="n">
+        <v>39185</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>256283</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Odontocolon appendiculatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Gravenhorst, 1829)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>malaisefälla</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SMTP Trap ID 42, Sånfjället, Nyvallens fäbod, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>425809</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6910280</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2004-07-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2004-08-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>alpine birch and spruce wood</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Svenska Malaisefälleprojektet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 174-2021 artfynd.xlsx
+++ b/artfynd/A 174-2021 artfynd.xlsx
@@ -3332,7 +3332,7 @@
         <v>121592572</v>
       </c>
       <c r="B26" t="n">
-        <v>39185</v>
+        <v>39186</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 174-2021 artfynd.xlsx
+++ b/artfynd/A 174-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3463,6 +3463,142 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121890407</v>
+      </c>
+      <c r="B27" t="n">
+        <v>23000</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>232185</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Urytalpa trivittata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Lundström, 1914)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>malaisefälla</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SMTP Trap ID 42, Sånfjället, Nyvallens fäbod, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>425809</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6910280</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2003-07-25</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2003-09-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>alpine birch and spruce wood</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Station Linné</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Svenska Malaisefälleprojektet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 174-2021 artfynd.xlsx
+++ b/artfynd/A 174-2021 artfynd.xlsx
@@ -3332,7 +3332,7 @@
         <v>121592572</v>
       </c>
       <c r="B26" t="n">
-        <v>39186</v>
+        <v>39191</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>121890407</v>
       </c>
       <c r="B27" t="n">
-        <v>23000</v>
+        <v>23003</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
